--- a/Config.xlsx
+++ b/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1abb604d7086dfb/Documents/GitHub/hrfc-welcome-pack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="254" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5540CD87-F0E9-48EE-8DAB-5829EC4E31C7}"/>
+  <xr:revisionPtr revIDLastSave="281" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF453607-5397-4713-95EE-86936813C136}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="4290" windowWidth="28155" windowHeight="15300" activeTab="1" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
+    <workbookView xWindow="22680" yWindow="735" windowWidth="28155" windowHeight="15300" activeTab="1" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
   </bookViews>
   <sheets>
     <sheet name="pitch_anchors" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="241">
   <si>
     <t>pitch_key</t>
   </si>
@@ -729,6 +729,42 @@
   </si>
   <si>
     <t>RRFC &amp; ARFC</t>
+  </si>
+  <si>
+    <t>file_comp</t>
+  </si>
+  <si>
+    <t>BKOC</t>
+  </si>
+  <si>
+    <t>GIRLS NATCUP</t>
+  </si>
+  <si>
+    <t>slug_alias</t>
+  </si>
+  <si>
+    <t>CNRFC</t>
+  </si>
+  <si>
+    <t>E&amp;RRFC</t>
+  </si>
+  <si>
+    <t>OQRFC</t>
+  </si>
+  <si>
+    <t>R&amp;A</t>
+  </si>
+  <si>
+    <t>RWBRFC</t>
+  </si>
+  <si>
+    <t>ROSES</t>
+  </si>
+  <si>
+    <t>LIONESSES</t>
+  </si>
+  <si>
+    <t>M&amp;C</t>
   </si>
 </sst>
 </file>
@@ -2110,15 +2146,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5837B33A-C646-4048-BB46-7ABB988B4ED9}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>54</v>
       </c>
@@ -2128,8 +2165,11 @@
       <c r="C1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -2139,8 +2179,12 @@
       <c r="C2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="str">
+        <f>LEFT(A2,1)&amp;"RFC"</f>
+        <v>ARFC</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -2150,8 +2194,12 @@
       <c r="C3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D44" si="0">LEFT(A3,1)&amp;"RFC"</f>
+        <v>BRFC</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>136</v>
       </c>
@@ -2161,8 +2209,12 @@
       <c r="C4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="str">
+        <f t="shared" si="0"/>
+        <v>BRFC</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>137</v>
       </c>
@@ -2172,8 +2224,12 @@
       <c r="C5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>BRFC</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>138</v>
       </c>
@@ -2183,8 +2239,12 @@
       <c r="C6" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>BRFC</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>139</v>
       </c>
@@ -2194,8 +2254,12 @@
       <c r="C7" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>CRFC</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>140</v>
       </c>
@@ -2205,8 +2269,11 @@
       <c r="C8" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>141</v>
       </c>
@@ -2216,8 +2283,12 @@
       <c r="C9" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>CRFC</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>142</v>
       </c>
@@ -2227,8 +2298,12 @@
       <c r="C10" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>CRFC</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>185</v>
       </c>
@@ -2238,8 +2313,11 @@
       <c r="C11" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>143</v>
       </c>
@@ -2249,8 +2327,11 @@
       <c r="C12" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>144</v>
       </c>
@@ -2260,8 +2341,12 @@
       <c r="C13" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" t="str">
+        <f t="shared" si="0"/>
+        <v>FRFC</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>78</v>
       </c>
@@ -2272,7 +2357,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>145</v>
       </c>
@@ -2282,8 +2367,12 @@
       <c r="C15" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v>FRFC</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>146</v>
       </c>
@@ -2293,8 +2382,12 @@
       <c r="C16" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>GRFC</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>147</v>
       </c>
@@ -2304,8 +2397,12 @@
       <c r="C17" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="str">
+        <f t="shared" si="0"/>
+        <v>GRFC</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>148</v>
       </c>
@@ -2315,8 +2412,12 @@
       <c r="C18" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="str">
+        <f t="shared" si="0"/>
+        <v>HRFC</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>149</v>
       </c>
@@ -2326,8 +2427,12 @@
       <c r="C19" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="str">
+        <f t="shared" si="0"/>
+        <v>MRFC</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>150</v>
       </c>
@@ -2337,8 +2442,12 @@
       <c r="C20" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="str">
+        <f t="shared" si="0"/>
+        <v>NRFC</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>151</v>
       </c>
@@ -2348,8 +2457,12 @@
       <c r="C21" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="str">
+        <f t="shared" si="0"/>
+        <v>ORFC</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>152</v>
       </c>
@@ -2359,8 +2472,12 @@
       <c r="C22" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="str">
+        <f t="shared" si="0"/>
+        <v>ORFC</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>153</v>
       </c>
@@ -2370,8 +2487,11 @@
       <c r="C23" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>154</v>
       </c>
@@ -2381,8 +2501,12 @@
       <c r="C24" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="str">
+        <f t="shared" si="0"/>
+        <v>PRFC</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>155</v>
       </c>
@@ -2392,8 +2516,12 @@
       <c r="C25" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="str">
+        <f t="shared" si="0"/>
+        <v>RRFC</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>156</v>
       </c>
@@ -2403,8 +2531,12 @@
       <c r="C26" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="str">
+        <f t="shared" si="0"/>
+        <v>RRFC</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -2414,8 +2546,11 @@
       <c r="C27" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>157</v>
       </c>
@@ -2425,8 +2560,11 @@
       <c r="C28" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>158</v>
       </c>
@@ -2436,8 +2574,12 @@
       <c r="C29" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="str">
+        <f t="shared" si="0"/>
+        <v>SRFC</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>159</v>
       </c>
@@ -2447,8 +2589,12 @@
       <c r="C30" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="str">
+        <f t="shared" si="0"/>
+        <v>SRFC</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>160</v>
       </c>
@@ -2458,8 +2604,12 @@
       <c r="C31" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="str">
+        <f t="shared" si="0"/>
+        <v>SRFC</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>167</v>
       </c>
@@ -2469,8 +2619,11 @@
       <c r="C32" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>115</v>
       </c>
@@ -2481,7 +2634,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>161</v>
       </c>
@@ -2491,8 +2644,12 @@
       <c r="C34" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="str">
+        <f t="shared" si="0"/>
+        <v>TRFC</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>162</v>
       </c>
@@ -2502,8 +2659,12 @@
       <c r="C35" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="str">
+        <f t="shared" si="0"/>
+        <v>TRFC</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>163</v>
       </c>
@@ -2513,8 +2674,12 @@
       <c r="C36" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="str">
+        <f t="shared" si="0"/>
+        <v>TRFC</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>164</v>
       </c>
@@ -2524,8 +2689,12 @@
       <c r="C37" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="str">
+        <f t="shared" si="0"/>
+        <v>WRFC</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>126</v>
       </c>
@@ -2535,8 +2704,12 @@
       <c r="C38" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="str">
+        <f t="shared" si="0"/>
+        <v>WRFC</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>165</v>
       </c>
@@ -2546,8 +2719,12 @@
       <c r="C39" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="str">
+        <f t="shared" si="0"/>
+        <v>WRFC</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>166</v>
       </c>
@@ -2557,8 +2734,12 @@
       <c r="C40" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="str">
+        <f t="shared" si="0"/>
+        <v>WRFC</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>132</v>
       </c>
@@ -2569,7 +2750,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>170</v>
       </c>
@@ -2579,8 +2760,11 @@
       <c r="C42" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>223</v>
       </c>
@@ -2590,8 +2774,11 @@
       <c r="C43" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>225</v>
       </c>
@@ -2600,6 +2787,9 @@
       </c>
       <c r="C44" t="s">
         <v>227</v>
+      </c>
+      <c r="D44" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -2609,7 +2799,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B104E4-035A-4BFE-8619-B4B38DDC79FD}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
@@ -2618,7 +2808,7 @@
     <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>186</v>
       </c>
@@ -2637,8 +2827,11 @@
       <c r="F1" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>187</v>
       </c>
@@ -2646,7 +2839,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>188</v>
       </c>
@@ -2654,7 +2847,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>189</v>
       </c>
@@ -2662,7 +2855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>190</v>
       </c>
@@ -2670,7 +2863,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>191</v>
       </c>
@@ -2678,7 +2871,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>192</v>
       </c>
@@ -2686,7 +2879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>193</v>
       </c>
@@ -2697,7 +2890,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>194</v>
       </c>
@@ -2716,8 +2909,11 @@
       <c r="F9">
         <v>50</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>195</v>
       </c>
@@ -2736,8 +2932,11 @@
       <c r="F10">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>195</v>
       </c>
@@ -2756,8 +2955,11 @@
       <c r="F11">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>196</v>
       </c>
@@ -2776,8 +2978,11 @@
       <c r="F12">
         <v>60</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>197</v>
       </c>
@@ -2796,8 +3001,11 @@
       <c r="F13">
         <v>70</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>198</v>
       </c>
@@ -2816,8 +3024,11 @@
       <c r="F14">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>199</v>
       </c>
@@ -2836,8 +3047,11 @@
       <c r="F15">
         <v>50</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>199</v>
       </c>
@@ -2856,8 +3070,11 @@
       <c r="F16">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>199</v>
       </c>
@@ -2876,8 +3093,11 @@
       <c r="F17">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>200</v>
       </c>
@@ -2896,8 +3116,11 @@
       <c r="F18">
         <v>60</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>200</v>
       </c>
@@ -2915,6 +3138,9 @@
       </c>
       <c r="F19">
         <v>60</v>
+      </c>
+      <c r="G19" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/Config.xlsx
+++ b/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1abb604d7086dfb/Documents/GitHub/hrfc-welcome-pack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="281" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF453607-5397-4713-95EE-86936813C136}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CE760B2-D84A-4E94-A0D0-CBEF843C3A42}"/>
   <bookViews>
-    <workbookView xWindow="22680" yWindow="735" windowWidth="28155" windowHeight="15300" activeTab="1" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
+    <workbookView xWindow="12195" yWindow="1080" windowWidth="28155" windowHeight="17790" activeTab="1" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
   </bookViews>
   <sheets>
     <sheet name="pitch_anchors" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="251">
   <si>
     <t>pitch_key</t>
   </si>
@@ -765,6 +765,36 @@
   </si>
   <si>
     <t>M&amp;C</t>
+  </si>
+  <si>
+    <t>Pewsey Vale RFC</t>
+  </si>
+  <si>
+    <t>Pewsey Vale</t>
+  </si>
+  <si>
+    <t>PEWSEY VALE</t>
+  </si>
+  <si>
+    <t>PVRFC</t>
+  </si>
+  <si>
+    <t>ARFC</t>
+  </si>
+  <si>
+    <t>ANDOVER</t>
+  </si>
+  <si>
+    <t>Andover RFC</t>
+  </si>
+  <si>
+    <t>Devizes RFC</t>
+  </si>
+  <si>
+    <t>DEVIZES</t>
+  </si>
+  <si>
+    <t>DRFC</t>
   </si>
 </sst>
 </file>
@@ -2146,7 +2176,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5837B33A-C646-4048-BB46-7ABB988B4ED9}">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" customWidth="1"/>
@@ -2186,613 +2216,658 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>247</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>247</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="str">
-        <f t="shared" ref="D3:D44" si="0">LEFT(A3,1)&amp;"RFC"</f>
-        <v>BRFC</v>
+        <v>246</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D4" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A4,1)&amp;"RFC"</f>
         <v>BRFC</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A5,1)&amp;"RFC"</f>
         <v>BRFC</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D6" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A6,1)&amp;"RFC"</f>
         <v>BRFC</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D7" t="str">
-        <f t="shared" si="0"/>
-        <v>CRFC</v>
+        <f>LEFT(A7,1)&amp;"RFC"</f>
+        <v>BRFC</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>233</v>
+        <v>68</v>
+      </c>
+      <c r="D8" t="str">
+        <f>LEFT(A8,1)&amp;"RFC"</f>
+        <v>CRFC</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" t="str">
-        <f t="shared" si="0"/>
-        <v>CRFC</v>
+        <v>69</v>
+      </c>
+      <c r="D9" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D10" t="str">
-        <f t="shared" si="0"/>
+        <f>LEFT(A10,1)&amp;"RFC"</f>
         <v>CRFC</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>234</v>
+        <v>73</v>
+      </c>
+      <c r="D12" t="str">
+        <f>LEFT(A12,1)&amp;"RFC"</f>
+        <v>CRFC</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>144</v>
+        <v>248</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>248</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" t="str">
-        <f t="shared" si="0"/>
-        <v>FRFC</v>
+        <v>249</v>
+      </c>
+      <c r="D13" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" t="str">
-        <f t="shared" si="0"/>
-        <v>FRFC</v>
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" t="str">
-        <f t="shared" si="0"/>
-        <v>GRFC</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D17" t="str">
-        <f t="shared" si="0"/>
-        <v>GRFC</v>
+        <f>LEFT(A17,1)&amp;"RFC"</f>
+        <v>FRFC</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D18" t="str">
-        <f t="shared" si="0"/>
-        <v>HRFC</v>
+        <f>LEFT(A18,1)&amp;"RFC"</f>
+        <v>FRFC</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D19" t="str">
-        <f t="shared" si="0"/>
-        <v>MRFC</v>
+        <f>LEFT(A19,1)&amp;"RFC"</f>
+        <v>GRFC</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D20" t="str">
-        <f t="shared" si="0"/>
-        <v>NRFC</v>
+        <f>LEFT(A20,1)&amp;"RFC"</f>
+        <v>GRFC</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D21" t="str">
-        <f t="shared" si="0"/>
-        <v>ORFC</v>
+        <f>LEFT(A21,1)&amp;"RFC"</f>
+        <v>HRFC</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D22" t="str">
-        <f t="shared" si="0"/>
-        <v>ORFC</v>
+        <f>LEFT(A22,1)&amp;"RFC"</f>
+        <v>MRFC</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>153</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>226</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c r="D23" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D24" t="str">
-        <f t="shared" si="0"/>
-        <v>PRFC</v>
+        <f>LEFT(A24,1)&amp;"RFC"</f>
+        <v>NRFC</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D25" t="str">
-        <f t="shared" si="0"/>
-        <v>RRFC</v>
+        <f>LEFT(A25,1)&amp;"RFC"</f>
+        <v>ORFC</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
-      </c>
-      <c r="D26" t="str">
-        <f t="shared" si="0"/>
-        <v>RRFC</v>
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s">
-        <v>228</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" t="s">
-        <v>236</v>
+        <v>95</v>
+      </c>
+      <c r="D27" t="str">
+        <f>LEFT(A27,1)&amp;"RFC"</f>
+        <v>ORFC</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B28" t="s">
-        <v>174</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" t="s">
-        <v>237</v>
+        <v>99</v>
+      </c>
+      <c r="D28" t="str">
+        <f>LEFT(A28,1)&amp;"RFC"</f>
+        <v>PRFC</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>158</v>
+        <v>241</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" t="str">
-        <f t="shared" si="0"/>
-        <v>SRFC</v>
+        <v>243</v>
+      </c>
+      <c r="D29" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D30" t="str">
-        <f t="shared" si="0"/>
-        <v>SRFC</v>
+        <f>LEFT(A30,1)&amp;"RFC"</f>
+        <v>RRFC</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>228</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="str">
-        <f t="shared" si="0"/>
-        <v>SRFC</v>
+        <v>105</v>
+      </c>
+      <c r="D31" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" t="s">
-        <v>238</v>
+        <v>103</v>
+      </c>
+      <c r="D32" t="str">
+        <f>LEFT(A32,1)&amp;"RFC"</f>
+        <v>RRFC</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>106</v>
+      </c>
+      <c r="D33" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D34" t="str">
-        <f t="shared" si="0"/>
-        <v>TRFC</v>
+        <f>LEFT(A34,1)&amp;"RFC"</f>
+        <v>SRFC</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D35" t="str">
-        <f t="shared" si="0"/>
-        <v>TRFC</v>
+        <f>LEFT(A35,1)&amp;"RFC"</f>
+        <v>SRFC</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="D36" t="str">
-        <f t="shared" si="0"/>
-        <v>TRFC</v>
+        <f>LEFT(A36,1)&amp;"RFC"</f>
+        <v>SRFC</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
-      </c>
-      <c r="D37" t="str">
-        <f t="shared" si="0"/>
-        <v>WRFC</v>
+        <v>114</v>
+      </c>
+      <c r="D37" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B38" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
-      </c>
-      <c r="D38" t="str">
-        <f t="shared" si="0"/>
-        <v>WRFC</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B39" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D39" t="str">
-        <f t="shared" si="0"/>
-        <v>WRFC</v>
+        <f>LEFT(A39,1)&amp;"RFC"</f>
+        <v>TRFC</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D40" t="str">
-        <f t="shared" si="0"/>
-        <v>WRFC</v>
+        <f>LEFT(A40,1)&amp;"RFC"</f>
+        <v>TRFC</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>123</v>
+      </c>
+      <c r="D41" t="str">
+        <f>LEFT(A41,1)&amp;"RFC"</f>
+        <v>TRFC</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="B42" t="s">
-        <v>171</v>
+        <v>223</v>
       </c>
       <c r="C42" t="s">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="D42" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="B43" t="s">
-        <v>223</v>
+        <v>124</v>
       </c>
       <c r="C43" t="s">
-        <v>224</v>
-      </c>
-      <c r="D43" t="s">
-        <v>224</v>
+        <v>125</v>
+      </c>
+      <c r="D43" t="str">
+        <f>LEFT(A43,1)&amp;"RFC"</f>
+        <v>WRFC</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>225</v>
+        <v>126</v>
       </c>
       <c r="B44" t="s">
-        <v>226</v>
+        <v>126</v>
       </c>
       <c r="C44" t="s">
-        <v>227</v>
-      </c>
-      <c r="D44" t="s">
-        <v>240</v>
+        <v>127</v>
+      </c>
+      <c r="D44" t="str">
+        <f>LEFT(A44,1)&amp;"RFC"</f>
+        <v>WRFC</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" t="s">
+        <v>128</v>
+      </c>
+      <c r="C45" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" t="str">
+        <f>LEFT(A45,1)&amp;"RFC"</f>
+        <v>WRFC</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>166</v>
+      </c>
+      <c r="B47" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" t="s">
+        <v>131</v>
+      </c>
+      <c r="D47" t="str">
+        <f>LEFT(A47,1)&amp;"RFC"</f>
+        <v>WRFC</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D47">
+    <sortCondition ref="A2:A47"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Config.xlsx
+++ b/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1abb604d7086dfb/Documents/GitHub/hrfc-welcome-pack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CE760B2-D84A-4E94-A0D0-CBEF843C3A42}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="8_{2B1AC583-5465-480E-8734-C5520FEC8B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D91E805-9286-4AA7-B916-B4CB4363FD09}"/>
   <bookViews>
-    <workbookView xWindow="12195" yWindow="1080" windowWidth="28155" windowHeight="17790" activeTab="1" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{F0613D2D-2141-47EF-8F8E-77ECD01D07A2}"/>
   </bookViews>
   <sheets>
     <sheet name="pitch_anchors" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="266">
   <si>
     <t>pitch_key</t>
   </si>
@@ -795,6 +795,51 @@
   </si>
   <si>
     <t>DRFC</t>
+  </si>
+  <si>
+    <t>Portsfield RFC</t>
+  </si>
+  <si>
+    <t>Portsfield</t>
+  </si>
+  <si>
+    <t>PORTSFIELD</t>
+  </si>
+  <si>
+    <t>Melksham Fawns</t>
+  </si>
+  <si>
+    <t>Fawns</t>
+  </si>
+  <si>
+    <t>MF</t>
+  </si>
+  <si>
+    <t>MELKSHAM FAWNS</t>
+  </si>
+  <si>
+    <t>Witney RFC</t>
+  </si>
+  <si>
+    <t>Witney</t>
+  </si>
+  <si>
+    <t>WITNEY</t>
+  </si>
+  <si>
+    <t>WRFC</t>
+  </si>
+  <si>
+    <t>DNQW</t>
+  </si>
+  <si>
+    <t>Didcot Newbury Quins Witney</t>
+  </si>
+  <si>
+    <t>Didcot RFC</t>
+  </si>
+  <si>
+    <t>DIDCOT</t>
   </si>
 </sst>
 </file>
@@ -2176,7 +2221,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5837B33A-C646-4048-BB46-7ABB988B4ED9}">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" customWidth="1"/>
@@ -2425,7 +2470,7 @@
         <v>77</v>
       </c>
       <c r="D17" t="str">
-        <f>LEFT(A17,1)&amp;"RFC"</f>
+        <f t="shared" ref="D17:D22" si="0">LEFT(A17,1)&amp;"RFC"</f>
         <v>FRFC</v>
       </c>
     </row>
@@ -2440,7 +2485,7 @@
         <v>82</v>
       </c>
       <c r="D18" t="str">
-        <f>LEFT(A18,1)&amp;"RFC"</f>
+        <f t="shared" si="0"/>
         <v>FRFC</v>
       </c>
     </row>
@@ -2455,7 +2500,7 @@
         <v>84</v>
       </c>
       <c r="D19" t="str">
-        <f>LEFT(A19,1)&amp;"RFC"</f>
+        <f t="shared" si="0"/>
         <v>GRFC</v>
       </c>
     </row>
@@ -2470,7 +2515,7 @@
         <v>86</v>
       </c>
       <c r="D20" t="str">
-        <f>LEFT(A20,1)&amp;"RFC"</f>
+        <f t="shared" si="0"/>
         <v>GRFC</v>
       </c>
     </row>
@@ -2485,7 +2530,7 @@
         <v>88</v>
       </c>
       <c r="D21" t="str">
-        <f>LEFT(A21,1)&amp;"RFC"</f>
+        <f t="shared" si="0"/>
         <v>HRFC</v>
       </c>
     </row>
@@ -2500,7 +2545,7 @@
         <v>90</v>
       </c>
       <c r="D22" t="str">
-        <f>LEFT(A22,1)&amp;"RFC"</f>
+        <f t="shared" si="0"/>
         <v>MRFC</v>
       </c>
     </row>
@@ -2862,6 +2907,78 @@
       <c r="D47" t="str">
         <f>LEFT(A47,1)&amp;"RFC"</f>
         <v>WRFC</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>251</v>
+      </c>
+      <c r="B48" t="s">
+        <v>252</v>
+      </c>
+      <c r="C48" t="s">
+        <v>253</v>
+      </c>
+      <c r="D48" t="str">
+        <f>LEFT(A48,1)&amp;"RFC"</f>
+        <v>PRFC</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>254</v>
+      </c>
+      <c r="B49" t="s">
+        <v>255</v>
+      </c>
+      <c r="C49" t="s">
+        <v>257</v>
+      </c>
+      <c r="D49" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>258</v>
+      </c>
+      <c r="B50" t="s">
+        <v>259</v>
+      </c>
+      <c r="C50" t="s">
+        <v>260</v>
+      </c>
+      <c r="D50" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>263</v>
+      </c>
+      <c r="B51" t="s">
+        <v>262</v>
+      </c>
+      <c r="C51" t="str">
+        <f>B51</f>
+        <v>DNQW</v>
+      </c>
+      <c r="D51" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>264</v>
+      </c>
+      <c r="B52" t="s">
+        <v>264</v>
+      </c>
+      <c r="C52" t="s">
+        <v>265</v>
+      </c>
+      <c r="D52" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
